--- a/results/master_proposed_threshold_results.xlsx
+++ b/results/master_proposed_threshold_results.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\COIN\ML_HDD2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{5AE3F6B8-466D-46ED-9831-4CC85C24432E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D70AD5-D250-4A4D-8DF9-AE1AF3A6CC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="15420"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_proposed_threshold_resul" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -37,15 +50,6 @@
     <t>Threshold</t>
   </si>
   <si>
-    <t>Precision</t>
-  </si>
-  <si>
-    <t>Recall</t>
-  </si>
-  <si>
-    <t>FAR</t>
-  </si>
-  <si>
     <t>LGBM</t>
   </si>
   <si>
@@ -65,10 +69,6 @@
   </si>
   <si>
     <t>TOSHIBA_20MG07ACA14TA</t>
-  </si>
-  <si>
-    <t>리드타임중앙값</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>리드타임 표준편차</t>
@@ -106,12 +106,28 @@
     <t>수냉</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>disk Precision</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>disk Recall</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>disk FAR</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Median LT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,14 +287,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -705,14 +713,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,33 +786,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표2" displayName="표2" ref="A1:J62" totalsRowCount="1">
-  <autoFilter ref="A1:J61"/>
-  <sortState ref="A2:J61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:J62" totalsRowCount="1">
+  <autoFilter ref="A1:J61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
     <sortCondition descending="1" ref="C1:C61"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" name="Timestamp" dataDxfId="1" totalsRowDxfId="0"/>
-    <tableColumn id="2" name="Model"/>
-    <tableColumn id="3" name="데이터"/>
-    <tableColumn id="4" name="Seed"/>
-    <tableColumn id="5" name="Threshold"/>
-    <tableColumn id="6" name="Precision"/>
-    <tableColumn id="7" name="Recall"/>
-    <tableColumn id="8" name="FAR"/>
-    <tableColumn id="9" name="리드타임중앙값" totalsRowFunction="custom">
-      <totalsRowFormula>AVERAGE(표2[리드타임중앙값])</totalsRowFormula>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Model"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="데이터"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Seed"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Threshold"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="disk Precision"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="disk Recall"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="disk FAR"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Median LT" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(표2[Median LT])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="리드타임 표준편차"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="리드타임 표준편차"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -845,7 +850,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -951,7 +956,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1093,14 +1098,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1134,22 +1139,22 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N1">
         <v>180</v>
@@ -1160,10 +1165,10 @@
         <v>46239</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>42</v>
@@ -1187,7 +1192,7 @@
         <v>46</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N2">
         <v>150</v>
@@ -1198,10 +1203,10 @@
         <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>43</v>
@@ -1225,7 +1230,7 @@
         <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N3">
         <v>70</v>
@@ -1236,10 +1241,10 @@
         <v>46239</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>44</v>
@@ -1263,7 +1268,7 @@
         <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N4">
         <v>180</v>
@@ -1274,10 +1279,10 @@
         <v>46239</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>45</v>
@@ -1301,7 +1306,7 @@
         <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N5">
         <v>30</v>
@@ -1312,10 +1317,10 @@
         <v>46239</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>46</v>
@@ -1339,7 +1344,7 @@
         <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -1350,10 +1355,10 @@
         <v>46239</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
       <c r="D7">
         <v>42</v>
@@ -1377,7 +1382,7 @@
         <v>52</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N7">
         <v>10</v>
@@ -1388,10 +1393,10 @@
         <v>46239</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -1415,7 +1420,7 @@
         <v>61.5</v>
       </c>
       <c r="M8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -1426,10 +1431,10 @@
         <v>46239</v>
       </c>
       <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
       <c r="D9">
         <v>44</v>
@@ -1458,10 +1463,10 @@
         <v>46239</v>
       </c>
       <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
       </c>
       <c r="D10">
         <v>45</v>
@@ -1490,10 +1495,10 @@
         <v>46239</v>
       </c>
       <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -1522,10 +1527,10 @@
         <v>46239</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>42</v>
@@ -1554,10 +1559,10 @@
         <v>46239</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <v>43</v>
@@ -1586,10 +1591,10 @@
         <v>46239</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>44</v>
@@ -1618,10 +1623,10 @@
         <v>46239</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>45</v>
@@ -1650,10 +1655,10 @@
         <v>46239</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16">
         <v>46</v>
@@ -1682,10 +1687,10 @@
         <v>46239</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>42</v>
@@ -1714,10 +1719,10 @@
         <v>46239</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>43</v>
@@ -1746,10 +1751,10 @@
         <v>46239</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19">
         <v>44</v>
@@ -1778,10 +1783,10 @@
         <v>46239</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>45</v>
@@ -1810,10 +1815,10 @@
         <v>46239</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21">
         <v>46</v>
@@ -1842,10 +1847,10 @@
         <v>46239</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>42</v>
@@ -1874,10 +1879,10 @@
         <v>46239</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>43</v>
@@ -1906,10 +1911,10 @@
         <v>46239</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>44</v>
@@ -1938,10 +1943,10 @@
         <v>46239</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>45</v>
@@ -1970,10 +1975,10 @@
         <v>46239</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>46</v>
@@ -2002,10 +2007,10 @@
         <v>46239</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>42</v>
@@ -2034,10 +2039,10 @@
         <v>46239</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>43</v>
@@ -2066,10 +2071,10 @@
         <v>46239</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>44</v>
@@ -2098,10 +2103,10 @@
         <v>46239</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>45</v>
@@ -2130,10 +2135,10 @@
         <v>46239</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>46</v>
@@ -2162,10 +2167,10 @@
         <v>46239</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>42</v>
@@ -2194,10 +2199,10 @@
         <v>46239</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>43</v>
@@ -2226,10 +2231,10 @@
         <v>46239</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>44</v>
@@ -2258,10 +2263,10 @@
         <v>46239</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>45</v>
@@ -2290,10 +2295,10 @@
         <v>46239</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>46</v>
@@ -2322,10 +2327,10 @@
         <v>46239</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>42</v>
@@ -2354,10 +2359,10 @@
         <v>46239</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>43</v>
@@ -2386,10 +2391,10 @@
         <v>46239</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>44</v>
@@ -2418,10 +2423,10 @@
         <v>46239</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>45</v>
@@ -2450,10 +2455,10 @@
         <v>46239</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>46</v>
@@ -2482,10 +2487,10 @@
         <v>46239</v>
       </c>
       <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
         <v>10</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
       </c>
       <c r="D42">
         <v>42</v>
@@ -2514,10 +2519,10 @@
         <v>46239</v>
       </c>
       <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
         <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
       </c>
       <c r="D43">
         <v>43</v>
@@ -2546,10 +2551,10 @@
         <v>46239</v>
       </c>
       <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
         <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>13</v>
       </c>
       <c r="D44">
         <v>44</v>
@@ -2578,10 +2583,10 @@
         <v>46239</v>
       </c>
       <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
         <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>13</v>
       </c>
       <c r="D45">
         <v>45</v>
@@ -2610,10 +2615,10 @@
         <v>46239</v>
       </c>
       <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
         <v>10</v>
-      </c>
-      <c r="C46" t="s">
-        <v>13</v>
       </c>
       <c r="D46">
         <v>46</v>
@@ -2642,10 +2647,10 @@
         <v>46239</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47">
         <v>42</v>
@@ -2674,10 +2679,10 @@
         <v>46239</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>43</v>
@@ -2706,10 +2711,10 @@
         <v>46239</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D49">
         <v>44</v>
@@ -2738,10 +2743,10 @@
         <v>46239</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D50">
         <v>45</v>
@@ -2770,10 +2775,10 @@
         <v>46239</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>46</v>
@@ -2802,10 +2807,10 @@
         <v>46239</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D52">
         <v>42</v>
@@ -2834,10 +2839,10 @@
         <v>46239</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D53">
         <v>43</v>
@@ -2866,10 +2871,10 @@
         <v>46239</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D54">
         <v>44</v>
@@ -2898,10 +2903,10 @@
         <v>46239</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D55">
         <v>45</v>
@@ -2930,10 +2935,10 @@
         <v>46239</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D56">
         <v>46</v>
@@ -2962,10 +2967,10 @@
         <v>46239</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D57">
         <v>42</v>
@@ -2994,10 +2999,10 @@
         <v>46239</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D58">
         <v>43</v>
@@ -3026,10 +3031,10 @@
         <v>46239</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>44</v>
@@ -3058,10 +3063,10 @@
         <v>46239</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D60">
         <v>45</v>
@@ -3090,10 +3095,10 @@
         <v>46239</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <v>46</v>
@@ -3120,7 +3125,7 @@
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="I62">
-        <f>AVERAGE(표2[리드타임중앙값])</f>
+        <f>AVERAGE(표2[Median LT])</f>
         <v>114.21066666666667</v>
       </c>
     </row>

--- a/results/master_proposed_threshold_results.xlsx
+++ b/results/master_proposed_threshold_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\COIN\ML_HDD2\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D70AD5-D250-4A4D-8DF9-AE1AF3A6CC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49F079E-846F-45AA-9548-0E9352642BBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,6 @@
     <sheet name="master_proposed_threshold_resul" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -288,7 +275,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,8 +455,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -584,6 +577,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -713,11 +741,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -788,8 +831,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:J62" totalsRowCount="1">
   <autoFilter ref="A1:J61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J61">
-    <sortCondition descending="1" ref="C1:C61"/>
+  <sortState ref="A2:J61">
+    <sortCondition ref="B1:B61"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp" dataDxfId="1" totalsRowDxfId="0"/>
@@ -810,9 +853,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -850,7 +893,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -956,7 +999,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1098,7 +1141,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1106,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1122,7 +1165,7 @@
     <col min="13" max="13" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1159,37 +1202,55 @@
       <c r="N1">
         <v>180</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S1" s="3">
+        <v>204.5</v>
+      </c>
+      <c r="U1" s="2">
+        <v>143.36000000000001</v>
+      </c>
+      <c r="W1">
+        <f>_xlfn.RANK.AVG(S1,S1:S60,0)</f>
+        <v>8</v>
+      </c>
+      <c r="X1">
+        <f>_xlfn.RANK.AVG(U1,U1:U60,0)</f>
+        <v>17</v>
+      </c>
+      <c r="Y1">
+        <f>CORREL(W1:W60,X1:X60)</f>
+        <v>0.79062828065614887</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46239</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>42</v>
       </c>
       <c r="E2">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F2">
-        <v>0.7177</v>
+        <v>0.75680000000000003</v>
       </c>
       <c r="G2">
-        <v>0.42580000000000001</v>
+        <v>0.34570000000000001</v>
       </c>
       <c r="H2">
-        <v>0.94</v>
+        <v>1.84</v>
       </c>
       <c r="I2">
-        <v>95.7</v>
+        <v>143.36000000000001</v>
       </c>
       <c r="J2">
-        <v>46</v>
+        <v>74.5</v>
       </c>
       <c r="M2" t="s">
         <v>14</v>
@@ -1197,37 +1258,51 @@
       <c r="N2">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S2" s="5">
+        <v>222</v>
+      </c>
+      <c r="U2" s="4">
+        <v>156.07</v>
+      </c>
+      <c r="W2">
+        <f t="shared" ref="W2:W60" si="0">_xlfn.RANK.AVG(S2,S2:S61,0)</f>
+        <v>5</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:X60" si="1">_xlfn.RANK.AVG(U2,U2:U61,0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
-        <v>0.73040000000000005</v>
+        <v>0.80279999999999996</v>
       </c>
       <c r="G3">
-        <v>0.40189999999999998</v>
+        <v>0.35189999999999999</v>
       </c>
       <c r="H3">
-        <v>0.83</v>
+        <v>1.43</v>
       </c>
       <c r="I3">
-        <v>92.23</v>
+        <v>156.07</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s">
         <v>15</v>
@@ -1235,16 +1310,30 @@
       <c r="N3">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S3" s="3">
+        <v>186</v>
+      </c>
+      <c r="U3" s="2">
+        <v>172.68</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46239</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>44</v>
@@ -1253,19 +1342,19 @@
         <v>0.13</v>
       </c>
       <c r="F4">
-        <v>0.70489999999999997</v>
+        <v>0.78669999999999995</v>
       </c>
       <c r="G4">
-        <v>0.41149999999999998</v>
+        <v>0.36420000000000002</v>
       </c>
       <c r="H4">
-        <v>0.97</v>
+        <v>1.64</v>
       </c>
       <c r="I4">
-        <v>100.42</v>
+        <v>172.68</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s">
         <v>16</v>
@@ -1273,37 +1362,51 @@
       <c r="N4">
         <v>180</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S4" s="5">
+        <v>206.5</v>
+      </c>
+      <c r="U4" s="4">
+        <v>148.1</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46239</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>45</v>
       </c>
       <c r="E5">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F5">
-        <v>0.72409999999999997</v>
+        <v>0.73129999999999995</v>
       </c>
       <c r="G5">
-        <v>0.40189999999999998</v>
+        <v>0.30249999999999999</v>
       </c>
       <c r="H5">
-        <v>0.86</v>
+        <v>1.84</v>
       </c>
       <c r="I5">
-        <v>86.82</v>
+        <v>148.1</v>
       </c>
       <c r="J5">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
         <v>17</v>
@@ -1311,37 +1414,51 @@
       <c r="N5">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S5" s="3">
+        <v>173</v>
+      </c>
+      <c r="U5" s="2">
+        <v>147.53</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46239</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>46</v>
       </c>
       <c r="E6">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F6">
-        <v>0.73599999999999999</v>
+        <v>0.78569999999999995</v>
       </c>
       <c r="G6">
-        <v>0.44019999999999998</v>
+        <v>0.33950000000000002</v>
       </c>
       <c r="H6">
-        <v>0.89</v>
+        <v>1.54</v>
       </c>
       <c r="I6">
-        <v>73.319999999999993</v>
+        <v>147.53</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
         <v>18</v>
@@ -1349,37 +1466,51 @@
       <c r="N6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S6" s="5">
+        <v>49</v>
+      </c>
+      <c r="U6" s="4">
+        <v>90.56</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46239</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>42</v>
       </c>
       <c r="E7">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="F7">
-        <v>0.70369999999999999</v>
+        <v>0.70589999999999997</v>
       </c>
       <c r="G7">
-        <v>0.36359999999999998</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H7">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="I7">
-        <v>82.82</v>
+        <v>90.56</v>
       </c>
       <c r="J7">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
         <v>19</v>
@@ -1387,37 +1518,51 @@
       <c r="N7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S7" s="3">
+        <v>44</v>
+      </c>
+      <c r="U7" s="2">
+        <v>101.62</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46239</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>43</v>
       </c>
       <c r="E8">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="F8">
-        <v>0.67889999999999995</v>
+        <v>0.69350000000000001</v>
       </c>
       <c r="G8">
-        <v>0.35410000000000003</v>
+        <v>0.38219999999999998</v>
       </c>
       <c r="H8">
-        <v>0.94</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>107.74</v>
+        <v>101.62</v>
       </c>
       <c r="J8">
-        <v>61.5</v>
+        <v>22</v>
       </c>
       <c r="M8" t="s">
         <v>20</v>
@@ -1425,109 +1570,165 @@
       <c r="N8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S8" s="5">
+        <v>48</v>
+      </c>
+      <c r="U8" s="4">
+        <v>100.75</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46239</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>44</v>
       </c>
       <c r="E9">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="F9">
-        <v>0.70799999999999996</v>
+        <v>0.7016</v>
       </c>
       <c r="G9">
-        <v>0.38279999999999997</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H9">
-        <v>0.89</v>
+        <v>1.01</v>
       </c>
       <c r="I9">
-        <v>88.79</v>
+        <v>100.75</v>
       </c>
       <c r="J9">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="S9" s="3">
+        <v>42</v>
+      </c>
+      <c r="U9" s="2">
+        <v>104.87</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46239</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>45</v>
       </c>
       <c r="E10">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="F10">
-        <v>0.75</v>
+        <v>0.75680000000000003</v>
       </c>
       <c r="G10">
-        <v>0.3589</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H10">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="I10">
-        <v>89.72</v>
+        <v>104.87</v>
       </c>
       <c r="J10">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>16.5</v>
+      </c>
+      <c r="S10" s="5">
+        <v>48</v>
+      </c>
+      <c r="U10" s="4">
+        <v>87.99</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46239</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>46</v>
       </c>
       <c r="E11">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="F11">
-        <v>0.73960000000000004</v>
+        <v>0.6583</v>
       </c>
       <c r="G11">
-        <v>0.3397</v>
+        <v>0.35110000000000002</v>
       </c>
       <c r="H11">
-        <v>0.67</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I11">
-        <v>93.24</v>
+        <v>87.99</v>
       </c>
       <c r="J11">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="S11" s="3">
+        <v>85.5</v>
+      </c>
+      <c r="U11" s="2">
+        <v>92.36</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46239</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -1536,30 +1737,44 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="F12">
-        <v>0.78949999999999998</v>
+        <v>0.72550000000000003</v>
       </c>
       <c r="G12">
-        <v>0.28710000000000002</v>
+        <v>0.35410000000000003</v>
       </c>
       <c r="H12">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="I12">
-        <v>90.12</v>
+        <v>92.36</v>
       </c>
       <c r="J12">
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>42.5</v>
+      </c>
+      <c r="S12" s="5">
+        <v>93</v>
+      </c>
+      <c r="U12" s="4">
+        <v>104.57</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46239</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -1568,30 +1783,44 @@
         <v>43</v>
       </c>
       <c r="E13">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>0.68140000000000001</v>
       </c>
       <c r="G13">
-        <v>0.36359999999999998</v>
+        <v>0.36840000000000001</v>
       </c>
       <c r="H13">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="I13">
-        <v>80.010000000000005</v>
+        <v>104.57</v>
       </c>
       <c r="J13">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="S13" s="3">
+        <v>87</v>
+      </c>
+      <c r="U13" s="2">
+        <v>97.49</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46239</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -1600,30 +1829,44 @@
         <v>44</v>
       </c>
       <c r="E14">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F14">
-        <v>0.7802</v>
+        <v>0.68469999999999998</v>
       </c>
       <c r="G14">
-        <v>0.3397</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H14">
-        <v>0.54</v>
+        <v>0.94</v>
       </c>
       <c r="I14">
-        <v>75.27</v>
+        <v>97.49</v>
       </c>
       <c r="J14">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="S14" s="5">
+        <v>86</v>
+      </c>
+      <c r="U14" s="4">
+        <v>86.55</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46239</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -1632,30 +1875,44 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F15">
-        <v>0.77659999999999996</v>
+        <v>0.70179999999999998</v>
       </c>
       <c r="G15">
-        <v>0.3493</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="H15">
-        <v>0.56000000000000005</v>
+        <v>0.91</v>
       </c>
       <c r="I15">
-        <v>78.38</v>
+        <v>86.55</v>
       </c>
       <c r="J15">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>44.5</v>
+      </c>
+      <c r="S15" s="3">
+        <v>83</v>
+      </c>
+      <c r="U15" s="2">
+        <v>91.39</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46239</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1664,190 +1921,274 @@
         <v>46</v>
       </c>
       <c r="E16">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F16">
-        <v>0.77659999999999996</v>
+        <v>0.73629999999999995</v>
       </c>
       <c r="G16">
-        <v>0.3493</v>
+        <v>0.3206</v>
       </c>
       <c r="H16">
-        <v>0.56000000000000005</v>
+        <v>0.64</v>
       </c>
       <c r="I16">
-        <v>78.38</v>
+        <v>91.39</v>
       </c>
       <c r="J16">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="S16" s="5">
+        <v>168</v>
+      </c>
+      <c r="U16" s="4">
+        <v>158.16</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46239</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>42</v>
       </c>
       <c r="E17">
-        <v>0.11</v>
+        <v>0.99</v>
       </c>
       <c r="F17">
-        <v>0.72550000000000003</v>
+        <v>0.77080000000000004</v>
       </c>
       <c r="G17">
-        <v>0.35410000000000003</v>
+        <v>0.22839999999999999</v>
       </c>
       <c r="H17">
-        <v>0.75</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I17">
-        <v>92.36</v>
+        <v>158.16</v>
       </c>
       <c r="J17">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="S17" s="3">
+        <v>169</v>
+      </c>
+      <c r="U17" s="2">
+        <v>167.08</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46239</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>43</v>
       </c>
       <c r="E18">
-        <v>0.09</v>
+        <v>0.78</v>
       </c>
       <c r="F18">
-        <v>0.68140000000000001</v>
+        <v>0.70909999999999995</v>
       </c>
       <c r="G18">
-        <v>0.36840000000000001</v>
+        <v>0.2407</v>
       </c>
       <c r="H18">
-        <v>0.97</v>
+        <v>1.64</v>
       </c>
       <c r="I18">
-        <v>104.57</v>
+        <v>167.08</v>
       </c>
       <c r="J18">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="S18" s="5">
+        <v>167.5</v>
+      </c>
+      <c r="U18" s="4">
+        <v>86.97</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46239</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>44</v>
       </c>
       <c r="E19">
-        <v>0.1</v>
+        <v>0.98</v>
       </c>
       <c r="F19">
-        <v>0.68469999999999998</v>
+        <v>0.76190000000000002</v>
       </c>
       <c r="G19">
-        <v>0.36359999999999998</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="H19">
-        <v>0.94</v>
+        <v>1.02</v>
       </c>
       <c r="I19">
-        <v>97.49</v>
+        <v>86.97</v>
       </c>
       <c r="J19">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="S19" s="3">
+        <v>134</v>
+      </c>
+      <c r="U19" s="2">
+        <v>152</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46239</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>45</v>
       </c>
       <c r="E20">
-        <v>0.12</v>
+        <v>0.91</v>
       </c>
       <c r="F20">
-        <v>0.70179999999999998</v>
+        <v>0.70830000000000004</v>
       </c>
       <c r="G20">
-        <v>0.38279999999999997</v>
+        <v>0.2099</v>
       </c>
       <c r="H20">
-        <v>0.91</v>
+        <v>1.43</v>
       </c>
       <c r="I20">
-        <v>86.55</v>
+        <v>152</v>
       </c>
       <c r="J20">
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>34.5</v>
+      </c>
+      <c r="S20" s="5">
+        <v>220.5</v>
+      </c>
+      <c r="U20" s="4">
+        <v>151.12</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46239</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>46</v>
       </c>
       <c r="E21">
-        <v>0.17</v>
+        <v>0.82</v>
       </c>
       <c r="F21">
-        <v>0.73629999999999995</v>
+        <v>0.75929999999999997</v>
       </c>
       <c r="G21">
-        <v>0.3206</v>
+        <v>0.25309999999999999</v>
       </c>
       <c r="H21">
-        <v>0.64</v>
+        <v>1.33</v>
       </c>
       <c r="I21">
-        <v>91.39</v>
+        <v>151.12</v>
       </c>
       <c r="J21">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="S21" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="U21" s="2">
+        <v>91.32</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46239</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
@@ -1856,30 +2197,44 @@
         <v>42</v>
       </c>
       <c r="E22">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="F22">
-        <v>0.69399999999999995</v>
+        <v>0.64290000000000003</v>
       </c>
       <c r="G22">
-        <v>0.4133</v>
+        <v>0.36</v>
       </c>
       <c r="H22">
-        <v>1.1200000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="I22">
-        <v>93.43</v>
+        <v>91.32</v>
       </c>
       <c r="J22">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="S22" s="5">
+        <v>34</v>
+      </c>
+      <c r="U22" s="4">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="0"/>
+        <v>35.5</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46239</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
@@ -1888,30 +2243,44 @@
         <v>43</v>
       </c>
       <c r="E23">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F23">
-        <v>0.71789999999999998</v>
+        <v>0.6512</v>
       </c>
       <c r="G23">
         <v>0.37330000000000002</v>
       </c>
       <c r="H23">
-        <v>0.9</v>
+        <v>1.23</v>
       </c>
       <c r="I23">
-        <v>92.4</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="J23">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>8.5</v>
+      </c>
+      <c r="S23" s="3">
+        <v>34</v>
+      </c>
+      <c r="U23" s="2">
+        <v>81.209999999999994</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46239</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
@@ -1920,30 +2289,44 @@
         <v>44</v>
       </c>
       <c r="E24">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="F24">
-        <v>0.66410000000000002</v>
+        <v>0.5484</v>
       </c>
       <c r="G24">
-        <v>0.38669999999999999</v>
+        <v>0.15110000000000001</v>
       </c>
       <c r="H24">
-        <v>1.2</v>
+        <v>0.77</v>
       </c>
       <c r="I24">
-        <v>99.25</v>
+        <v>81.209999999999994</v>
       </c>
       <c r="J24">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10.5</v>
+      </c>
+      <c r="S24" s="5">
+        <v>30</v>
+      </c>
+      <c r="U24" s="4">
+        <v>86.24</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46239</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
@@ -1952,30 +2335,44 @@
         <v>45</v>
       </c>
       <c r="E25">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="F25">
-        <v>0.6694</v>
+        <v>0.69169999999999998</v>
       </c>
       <c r="G25">
         <v>0.36890000000000001</v>
       </c>
       <c r="H25">
-        <v>1.1200000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="I25">
-        <v>97.96</v>
+        <v>86.24</v>
       </c>
       <c r="J25">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="S25" s="3">
+        <v>26</v>
+      </c>
+      <c r="U25" s="2">
+        <v>77.62</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46239</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
@@ -1984,350 +2381,504 @@
         <v>46</v>
       </c>
       <c r="E26">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F26">
-        <v>0.7319</v>
+        <v>0.67030000000000001</v>
       </c>
       <c r="G26">
-        <v>0.44890000000000002</v>
+        <v>0.27110000000000001</v>
       </c>
       <c r="H26">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="I26">
-        <v>102.67</v>
+        <v>77.62</v>
       </c>
       <c r="J26">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="S26" s="5">
+        <v>65</v>
+      </c>
+      <c r="U26" s="4">
+        <v>90.12</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46239</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D27">
         <v>42</v>
       </c>
       <c r="E27">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="F27">
-        <v>0.64459999999999995</v>
+        <v>0.78949999999999998</v>
       </c>
       <c r="G27">
-        <v>0.34670000000000001</v>
+        <v>0.28710000000000002</v>
       </c>
       <c r="H27">
-        <v>1.18</v>
+        <v>0.43</v>
       </c>
       <c r="I27">
-        <v>118.59</v>
+        <v>90.12</v>
       </c>
       <c r="J27">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>69.5</v>
+      </c>
+      <c r="S27" s="3">
+        <v>51</v>
+      </c>
+      <c r="U27" s="2">
+        <v>80.010000000000005</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46239</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D28">
         <v>43</v>
       </c>
       <c r="E28">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="F28">
-        <v>0.72809999999999997</v>
+        <v>0.8</v>
       </c>
       <c r="G28">
-        <v>0.36890000000000001</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H28">
-        <v>0.85</v>
+        <v>0.51</v>
       </c>
       <c r="I28">
-        <v>110.72</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="J28">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="S28" s="5">
+        <v>47</v>
+      </c>
+      <c r="U28" s="4">
+        <v>75.27</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46239</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D29">
         <v>44</v>
       </c>
       <c r="E29">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="F29">
-        <v>0.67330000000000001</v>
+        <v>0.7802</v>
       </c>
       <c r="G29">
-        <v>0.30220000000000002</v>
+        <v>0.3397</v>
       </c>
       <c r="H29">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="I29">
-        <v>103.44</v>
+        <v>75.27</v>
       </c>
       <c r="J29">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="S29" s="3">
+        <v>51</v>
+      </c>
+      <c r="U29" s="2">
+        <v>78.38</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="1"/>
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46239</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D30">
         <v>45</v>
       </c>
       <c r="E30">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="F30">
-        <v>0.64290000000000003</v>
+        <v>0.77659999999999996</v>
       </c>
       <c r="G30">
-        <v>0.32</v>
+        <v>0.3493</v>
       </c>
       <c r="H30">
-        <v>1.0900000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I30">
-        <v>127.1</v>
+        <v>78.38</v>
       </c>
       <c r="J30">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="S30" s="5">
+        <v>51</v>
+      </c>
+      <c r="U30" s="4">
+        <v>78.38</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46239</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D31">
         <v>46</v>
       </c>
       <c r="E31">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="F31">
-        <v>0.68930000000000002</v>
+        <v>0.77659999999999996</v>
       </c>
       <c r="G31">
-        <v>0.31559999999999999</v>
+        <v>0.3493</v>
       </c>
       <c r="H31">
-        <v>0.88</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I31">
-        <v>104.62</v>
+        <v>78.38</v>
       </c>
       <c r="J31">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="S31" s="3">
+        <v>174</v>
+      </c>
+      <c r="U31" s="2">
+        <v>176.85</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46239</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>42</v>
       </c>
       <c r="E32">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F32">
-        <v>0.64290000000000003</v>
+        <v>0.84379999999999999</v>
       </c>
       <c r="G32">
-        <v>0.36</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H32">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="I32">
-        <v>91.32</v>
+        <v>176.85</v>
       </c>
       <c r="J32">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="S32" s="5">
+        <v>158</v>
+      </c>
+      <c r="U32" s="4">
+        <v>155.13</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X32">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46239</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>43</v>
       </c>
       <c r="E33">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F33">
-        <v>0.6512</v>
+        <v>0.79410000000000003</v>
       </c>
       <c r="G33">
-        <v>0.37330000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H33">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="I33">
-        <v>76.900000000000006</v>
+        <v>155.13</v>
       </c>
       <c r="J33">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="S33" s="3">
+        <v>174</v>
+      </c>
+      <c r="U33" s="2">
+        <v>192.02</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46239</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>44</v>
       </c>
       <c r="E34">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="F34">
-        <v>0.5484</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="G34">
-        <v>0.15110000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H34">
-        <v>0.77</v>
+        <v>1.33</v>
       </c>
       <c r="I34">
-        <v>81.209999999999994</v>
+        <v>192.02</v>
       </c>
       <c r="J34">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>84.5</v>
+      </c>
+      <c r="S34" s="5">
+        <v>186.5</v>
+      </c>
+      <c r="U34" s="4">
+        <v>186.33</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46239</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>45</v>
       </c>
       <c r="E35">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F35">
-        <v>0.69169999999999998</v>
+        <v>0.81820000000000004</v>
       </c>
       <c r="G35">
-        <v>0.36890000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H35">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="I35">
-        <v>86.24</v>
+        <v>186.33</v>
       </c>
       <c r="J35">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>83.5</v>
+      </c>
+      <c r="S35" s="3">
+        <v>168</v>
+      </c>
+      <c r="U35" s="2">
+        <v>180.27</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46239</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>46</v>
       </c>
       <c r="E36">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F36">
-        <v>0.67030000000000001</v>
+        <v>0.7671</v>
       </c>
       <c r="G36">
-        <v>0.27110000000000001</v>
+        <v>0.34570000000000001</v>
       </c>
       <c r="H36">
-        <v>0.82</v>
+        <v>1.74</v>
       </c>
       <c r="I36">
-        <v>77.62</v>
+        <v>180.27</v>
       </c>
       <c r="J36">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>82.5</v>
+      </c>
+      <c r="S36" s="5">
+        <v>37.5</v>
+      </c>
+      <c r="U36" s="4">
+        <v>118.59</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X36">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46239</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
         <v>6</v>
@@ -2336,30 +2887,44 @@
         <v>42</v>
       </c>
       <c r="E37">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="F37">
-        <v>0.70589999999999997</v>
+        <v>0.64459999999999995</v>
       </c>
       <c r="G37">
-        <v>0.37330000000000002</v>
+        <v>0.34670000000000001</v>
       </c>
       <c r="H37">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="I37">
-        <v>90.56</v>
+        <v>118.59</v>
       </c>
       <c r="J37">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="S37" s="3">
+        <v>47</v>
+      </c>
+      <c r="U37" s="2">
+        <v>110.72</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="X37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46239</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
@@ -2371,27 +2936,41 @@
         <v>0.33</v>
       </c>
       <c r="F38">
-        <v>0.69350000000000001</v>
+        <v>0.72809999999999997</v>
       </c>
       <c r="G38">
-        <v>0.38219999999999998</v>
+        <v>0.36890000000000001</v>
       </c>
       <c r="H38">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="I38">
-        <v>101.62</v>
+        <v>110.72</v>
       </c>
       <c r="J38">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="S38" s="5">
+        <v>46</v>
+      </c>
+      <c r="U38" s="4">
+        <v>103.44</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="X38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46239</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
         <v>6</v>
@@ -2400,30 +2979,44 @@
         <v>44</v>
       </c>
       <c r="E39">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F39">
-        <v>0.7016</v>
+        <v>0.67330000000000001</v>
       </c>
       <c r="G39">
-        <v>0.38669999999999999</v>
+        <v>0.30220000000000002</v>
       </c>
       <c r="H39">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="I39">
-        <v>100.75</v>
+        <v>103.44</v>
       </c>
       <c r="J39">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>20.5</v>
+      </c>
+      <c r="S39" s="3">
+        <v>48.5</v>
+      </c>
+      <c r="U39" s="2">
+        <v>127.1</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="X39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46239</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
         <v>6</v>
@@ -2435,27 +3028,41 @@
         <v>0.31</v>
       </c>
       <c r="F40">
-        <v>0.75680000000000003</v>
+        <v>0.64290000000000003</v>
       </c>
       <c r="G40">
-        <v>0.37330000000000002</v>
+        <v>0.32</v>
       </c>
       <c r="H40">
-        <v>0.74</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I40">
-        <v>104.87</v>
+        <v>127.1</v>
       </c>
       <c r="J40">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="S40" s="5">
+        <v>49</v>
+      </c>
+      <c r="U40" s="4">
+        <v>104.62</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="X40">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46239</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
         <v>6</v>
@@ -2464,190 +3071,274 @@
         <v>46</v>
       </c>
       <c r="E41">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="F41">
-        <v>0.6583</v>
+        <v>0.68930000000000002</v>
       </c>
       <c r="G41">
-        <v>0.35110000000000002</v>
+        <v>0.31559999999999999</v>
       </c>
       <c r="H41">
-        <v>1.1200000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="I41">
-        <v>87.99</v>
+        <v>104.62</v>
       </c>
       <c r="J41">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="S41" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="U41" s="2">
+        <v>82.82</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X41">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46239</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42">
         <v>42</v>
       </c>
       <c r="E42">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="F42">
-        <v>0.78049999999999997</v>
+        <v>0.70369999999999999</v>
       </c>
       <c r="G42">
-        <v>0.19750000000000001</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H42">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I42">
-        <v>119.44</v>
+        <v>82.82</v>
       </c>
       <c r="J42">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="S42" s="5">
+        <v>92</v>
+      </c>
+      <c r="U42" s="4">
+        <v>107.74</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X42">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46239</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43">
         <v>43</v>
       </c>
       <c r="E43">
-        <v>0.44</v>
+        <v>0.16</v>
       </c>
       <c r="F43">
-        <v>0.77590000000000003</v>
+        <v>0.67889999999999995</v>
       </c>
       <c r="G43">
-        <v>0.27779999999999999</v>
+        <v>0.35410000000000003</v>
       </c>
       <c r="H43">
-        <v>1.33</v>
+        <v>0.94</v>
       </c>
       <c r="I43">
-        <v>153.16</v>
+        <v>107.74</v>
       </c>
       <c r="J43">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>61.5</v>
+      </c>
+      <c r="S43" s="3">
+        <v>85</v>
+      </c>
+      <c r="U43" s="2">
+        <v>88.79</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X43">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46239</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44">
         <v>44</v>
       </c>
       <c r="E44">
-        <v>0.52</v>
+        <v>0.17</v>
       </c>
       <c r="F44">
-        <v>0.80559999999999998</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="G44">
-        <v>0.17899999999999999</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="H44">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="I44">
-        <v>133.66</v>
+        <v>88.79</v>
       </c>
       <c r="J44">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>50.5</v>
+      </c>
+      <c r="S44" s="5">
+        <v>90</v>
+      </c>
+      <c r="U44" s="4">
+        <v>89.72</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X44">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46239</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45">
         <v>45</v>
       </c>
       <c r="E45">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="F45">
-        <v>0.8085</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
-        <v>0.2346</v>
+        <v>0.3589</v>
       </c>
       <c r="H45">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="I45">
-        <v>168.13</v>
+        <v>89.72</v>
       </c>
       <c r="J45">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="S45" s="3">
+        <v>88</v>
+      </c>
+      <c r="U45" s="2">
+        <v>93.24</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X45">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46239</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46">
         <v>46</v>
       </c>
       <c r="E46">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="F46">
-        <v>0.77359999999999995</v>
+        <v>0.73960000000000004</v>
       </c>
       <c r="G46">
-        <v>0.25309999999999999</v>
+        <v>0.3397</v>
       </c>
       <c r="H46">
-        <v>1.23</v>
+        <v>0.67</v>
       </c>
       <c r="I46">
-        <v>170</v>
+        <v>93.24</v>
       </c>
       <c r="J46">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="S46" s="5">
+        <v>223</v>
+      </c>
+      <c r="U46" s="4">
+        <v>119.44</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X46">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46239</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -2656,30 +3347,44 @@
         <v>42</v>
       </c>
       <c r="E47">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="F47">
-        <v>0.84379999999999999</v>
+        <v>0.78049999999999997</v>
       </c>
       <c r="G47">
-        <v>0.33329999999999999</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="H47">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="I47">
-        <v>176.85</v>
+        <v>119.44</v>
       </c>
       <c r="J47">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+        <v>40.5</v>
+      </c>
+      <c r="S47" s="3">
+        <v>243</v>
+      </c>
+      <c r="U47" s="2">
+        <v>153.16</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X47">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46239</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -2688,30 +3393,44 @@
         <v>43</v>
       </c>
       <c r="E48">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="F48">
-        <v>0.79410000000000003</v>
+        <v>0.77590000000000003</v>
       </c>
       <c r="G48">
-        <v>0.33329999999999999</v>
+        <v>0.27779999999999999</v>
       </c>
       <c r="H48">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="I48">
-        <v>155.13</v>
+        <v>153.16</v>
       </c>
       <c r="J48">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="S48" s="5">
+        <v>184</v>
+      </c>
+      <c r="U48" s="4">
+        <v>133.66</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X48">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46239</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -2720,30 +3439,44 @@
         <v>44</v>
       </c>
       <c r="E49">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="F49">
-        <v>0.80600000000000005</v>
+        <v>0.80559999999999998</v>
       </c>
       <c r="G49">
-        <v>0.33329999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="H49">
-        <v>1.33</v>
+        <v>0.72</v>
       </c>
       <c r="I49">
-        <v>192.02</v>
+        <v>133.66</v>
       </c>
       <c r="J49">
-        <v>84.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="S49" s="3">
+        <v>229</v>
+      </c>
+      <c r="U49" s="2">
+        <v>168.13</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46239</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -2752,30 +3485,44 @@
         <v>45</v>
       </c>
       <c r="E50">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F50">
-        <v>0.81820000000000004</v>
+        <v>0.8085</v>
       </c>
       <c r="G50">
-        <v>0.33329999999999999</v>
+        <v>0.2346</v>
       </c>
       <c r="H50">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="I50">
-        <v>186.33</v>
+        <v>168.13</v>
       </c>
       <c r="J50">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="S50" s="5">
+        <v>246</v>
+      </c>
+      <c r="U50" s="4">
+        <v>170</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46239</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -2784,257 +3531,369 @@
         <v>46</v>
       </c>
       <c r="E51">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="F51">
-        <v>0.7671</v>
+        <v>0.77359999999999995</v>
       </c>
       <c r="G51">
-        <v>0.34570000000000001</v>
+        <v>0.25309999999999999</v>
       </c>
       <c r="H51">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="I51">
-        <v>180.27</v>
+        <v>170</v>
       </c>
       <c r="J51">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="S51" s="3">
+        <v>30.5</v>
+      </c>
+      <c r="U51" s="2">
+        <v>93.43</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X51">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46239</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D52">
         <v>42</v>
       </c>
       <c r="E52">
-        <v>0.99</v>
+        <v>0.11</v>
       </c>
       <c r="F52">
-        <v>0.77080000000000004</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="G52">
-        <v>0.22839999999999999</v>
+        <v>0.4133</v>
       </c>
       <c r="H52">
-        <v>1.1299999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I52">
-        <v>158.16</v>
+        <v>93.43</v>
       </c>
       <c r="J52">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="S52" s="5">
+        <v>39</v>
+      </c>
+      <c r="U52" s="4">
+        <v>92.4</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X52">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46239</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>43</v>
       </c>
       <c r="E53">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="F53">
-        <v>0.70909999999999995</v>
+        <v>0.71789999999999998</v>
       </c>
       <c r="G53">
-        <v>0.2407</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H53">
-        <v>1.64</v>
+        <v>0.9</v>
       </c>
       <c r="I53">
-        <v>167.08</v>
+        <v>92.4</v>
       </c>
       <c r="J53">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+        <v>12.5</v>
+      </c>
+      <c r="S53" s="3">
+        <v>36</v>
+      </c>
+      <c r="U53" s="2">
+        <v>99.25</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X53">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46239</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>44</v>
       </c>
       <c r="E54">
-        <v>0.98</v>
+        <v>0.11</v>
       </c>
       <c r="F54">
-        <v>0.76190000000000002</v>
+        <v>0.66410000000000002</v>
       </c>
       <c r="G54">
-        <v>0.19750000000000001</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H54">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="I54">
-        <v>86.97</v>
+        <v>99.25</v>
       </c>
       <c r="J54">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="S54" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="U54" s="4">
+        <v>97.96</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46239</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>45</v>
       </c>
       <c r="E55">
-        <v>0.91</v>
+        <v>0.12</v>
       </c>
       <c r="F55">
-        <v>0.70830000000000004</v>
+        <v>0.6694</v>
       </c>
       <c r="G55">
-        <v>0.2099</v>
+        <v>0.36890000000000001</v>
       </c>
       <c r="H55">
-        <v>1.43</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I55">
-        <v>152</v>
+        <v>97.96</v>
       </c>
       <c r="J55">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="S55" s="3">
+        <v>37</v>
+      </c>
+      <c r="U55" s="2">
+        <v>102.67</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X55">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46239</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>46</v>
       </c>
       <c r="E56">
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="F56">
-        <v>0.75929999999999997</v>
+        <v>0.7319</v>
       </c>
       <c r="G56">
-        <v>0.25309999999999999</v>
+        <v>0.44890000000000002</v>
       </c>
       <c r="H56">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="I56">
-        <v>151.12</v>
+        <v>102.67</v>
       </c>
       <c r="J56">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="S56" s="5">
+        <v>71</v>
+      </c>
+      <c r="U56" s="4">
+        <v>95.7</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X56">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46239</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57">
         <v>42</v>
       </c>
       <c r="E57">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F57">
-        <v>0.75680000000000003</v>
+        <v>0.7177</v>
       </c>
       <c r="G57">
-        <v>0.34570000000000001</v>
+        <v>0.42580000000000001</v>
       </c>
       <c r="H57">
-        <v>1.84</v>
+        <v>0.94</v>
       </c>
       <c r="I57">
-        <v>143.36000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="J57">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="S57" s="3">
+        <v>67</v>
+      </c>
+      <c r="U57" s="2">
+        <v>92.23</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X57">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46239</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58">
         <v>43</v>
       </c>
       <c r="E58">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="F58">
-        <v>0.80279999999999996</v>
+        <v>0.73040000000000005</v>
       </c>
       <c r="G58">
-        <v>0.35189999999999999</v>
+        <v>0.40189999999999998</v>
       </c>
       <c r="H58">
-        <v>1.43</v>
+        <v>0.83</v>
       </c>
       <c r="I58">
-        <v>156.07</v>
+        <v>92.23</v>
       </c>
       <c r="J58">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="S58" s="5">
+        <v>72.5</v>
+      </c>
+      <c r="U58" s="4">
+        <v>100.42</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X58">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46239</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59">
         <v>44</v>
@@ -3043,90 +3902,122 @@
         <v>0.13</v>
       </c>
       <c r="F59">
-        <v>0.78669999999999995</v>
+        <v>0.70489999999999997</v>
       </c>
       <c r="G59">
-        <v>0.36420000000000002</v>
+        <v>0.41149999999999998</v>
       </c>
       <c r="H59">
-        <v>1.64</v>
+        <v>0.97</v>
       </c>
       <c r="I59">
-        <v>172.68</v>
+        <v>100.42</v>
       </c>
       <c r="J59">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="S59" s="3">
+        <v>61.5</v>
+      </c>
+      <c r="U59" s="2">
+        <v>86.82</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X59">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46239</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60">
         <v>45</v>
       </c>
       <c r="E60">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="F60">
-        <v>0.73129999999999995</v>
+        <v>0.72409999999999997</v>
       </c>
       <c r="G60">
-        <v>0.30249999999999999</v>
+        <v>0.40189999999999998</v>
       </c>
       <c r="H60">
-        <v>1.84</v>
+        <v>0.86</v>
       </c>
       <c r="I60">
-        <v>148.1</v>
+        <v>86.82</v>
       </c>
       <c r="J60">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="S60" s="5">
+        <v>65</v>
+      </c>
+      <c r="U60" s="4">
+        <v>73.319999999999993</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X60">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46239</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D61">
         <v>46</v>
       </c>
       <c r="E61">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="F61">
-        <v>0.78569999999999995</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="G61">
-        <v>0.33950000000000002</v>
+        <v>0.44019999999999998</v>
       </c>
       <c r="H61">
-        <v>1.54</v>
+        <v>0.89</v>
       </c>
       <c r="I61">
-        <v>147.53</v>
+        <v>73.319999999999993</v>
       </c>
       <c r="J61">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="U61" s="6">
+        <f>AVERAGE(표2[Median LT])</f>
+        <v>114.21066666666664</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="I62">
         <f>AVERAGE(표2[Median LT])</f>
-        <v>114.21066666666667</v>
+        <v>114.21066666666664</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_proposed_threshold_results.xlsx
+++ b/results/master_proposed_threshold_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\이데아\ML_HDD2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49F079E-846F-45AA-9548-0E9352642BBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026406F9-52D4-43F6-8D94-60ECF6526A6F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -832,7 +832,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표2" displayName="표2" ref="A1:J62" totalsRowCount="1">
   <autoFilter ref="A1:J61" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState ref="A2:J61">
-    <sortCondition ref="B1:B61"/>
+    <sortCondition ref="D1:D61"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp" dataDxfId="1" totalsRowDxfId="0"/>
@@ -1226,31 +1226,31 @@
         <v>46239</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>42</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F2">
-        <v>0.75680000000000003</v>
+        <v>0.7177</v>
       </c>
       <c r="G2">
-        <v>0.34570000000000001</v>
+        <v>0.42580000000000001</v>
       </c>
       <c r="H2">
-        <v>1.84</v>
+        <v>0.94</v>
       </c>
       <c r="I2">
-        <v>143.36000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="J2">
-        <v>74.5</v>
+        <v>46</v>
       </c>
       <c r="M2" t="s">
         <v>14</v>
@@ -1278,31 +1278,31 @@
         <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F3">
-        <v>0.80279999999999996</v>
+        <v>0.70369999999999999</v>
       </c>
       <c r="G3">
-        <v>0.35189999999999999</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H3">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="I3">
-        <v>156.07</v>
+        <v>82.82</v>
       </c>
       <c r="J3">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
         <v>15</v>
@@ -1330,31 +1330,31 @@
         <v>46239</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0.13</v>
       </c>
       <c r="F4">
-        <v>0.78669999999999995</v>
+        <v>0.78949999999999998</v>
       </c>
       <c r="G4">
-        <v>0.36420000000000002</v>
+        <v>0.28710000000000002</v>
       </c>
       <c r="H4">
-        <v>1.64</v>
+        <v>0.43</v>
       </c>
       <c r="I4">
-        <v>172.68</v>
+        <v>90.12</v>
       </c>
       <c r="J4">
-        <v>82</v>
+        <v>69.5</v>
       </c>
       <c r="M4" t="s">
         <v>16</v>
@@ -1385,28 +1385,28 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="F5">
-        <v>0.73129999999999995</v>
+        <v>0.72550000000000003</v>
       </c>
       <c r="G5">
-        <v>0.30249999999999999</v>
+        <v>0.35410000000000003</v>
       </c>
       <c r="H5">
-        <v>1.84</v>
+        <v>0.75</v>
       </c>
       <c r="I5">
-        <v>148.1</v>
+        <v>92.36</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>42.5</v>
       </c>
       <c r="M5" t="s">
         <v>17</v>
@@ -1434,31 +1434,31 @@
         <v>46239</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="F6">
-        <v>0.78569999999999995</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="G6">
-        <v>0.33950000000000002</v>
+        <v>0.4133</v>
       </c>
       <c r="H6">
-        <v>1.54</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I6">
-        <v>147.53</v>
+        <v>93.43</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="M6" t="s">
         <v>18</v>
@@ -1486,7 +1486,7 @@
         <v>46239</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -1495,22 +1495,22 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="F7">
-        <v>0.70589999999999997</v>
+        <v>0.64459999999999995</v>
       </c>
       <c r="G7">
-        <v>0.37330000000000002</v>
+        <v>0.34670000000000001</v>
       </c>
       <c r="H7">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="I7">
-        <v>90.56</v>
+        <v>118.59</v>
       </c>
       <c r="J7">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
         <v>19</v>
@@ -1538,31 +1538,31 @@
         <v>46239</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="F8">
-        <v>0.69350000000000001</v>
+        <v>0.64290000000000003</v>
       </c>
       <c r="G8">
-        <v>0.38219999999999998</v>
+        <v>0.36</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I8">
-        <v>101.62</v>
+        <v>91.32</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
         <v>20</v>
@@ -1596,25 +1596,25 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="F9">
-        <v>0.7016</v>
+        <v>0.70589999999999997</v>
       </c>
       <c r="G9">
-        <v>0.38669999999999999</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="I9">
-        <v>100.75</v>
+        <v>90.56</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S9" s="3">
         <v>42</v>
@@ -1636,31 +1636,31 @@
         <v>46239</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E10">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="F10">
-        <v>0.75680000000000003</v>
+        <v>0.78049999999999997</v>
       </c>
       <c r="G10">
-        <v>0.37330000000000002</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="H10">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="I10">
-        <v>104.87</v>
+        <v>119.44</v>
       </c>
       <c r="J10">
-        <v>16.5</v>
+        <v>40.5</v>
       </c>
       <c r="S10" s="5">
         <v>48</v>
@@ -1682,31 +1682,31 @@
         <v>46239</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E11">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="F11">
-        <v>0.6583</v>
+        <v>0.84379999999999999</v>
       </c>
       <c r="G11">
-        <v>0.35110000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H11">
-        <v>1.1200000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="I11">
-        <v>87.99</v>
+        <v>176.85</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="S11" s="3">
         <v>85.5</v>
@@ -1728,31 +1728,31 @@
         <v>46239</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>42</v>
       </c>
       <c r="E12">
-        <v>0.11</v>
+        <v>0.99</v>
       </c>
       <c r="F12">
-        <v>0.72550000000000003</v>
+        <v>0.77080000000000004</v>
       </c>
       <c r="G12">
-        <v>0.35410000000000003</v>
+        <v>0.22839999999999999</v>
       </c>
       <c r="H12">
-        <v>0.75</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I12">
-        <v>92.36</v>
+        <v>158.16</v>
       </c>
       <c r="J12">
-        <v>42.5</v>
+        <v>37</v>
       </c>
       <c r="S12" s="5">
         <v>93</v>
@@ -1777,28 +1777,28 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="F13">
-        <v>0.68140000000000001</v>
+        <v>0.75680000000000003</v>
       </c>
       <c r="G13">
-        <v>0.36840000000000001</v>
+        <v>0.34570000000000001</v>
       </c>
       <c r="H13">
-        <v>0.97</v>
+        <v>1.84</v>
       </c>
       <c r="I13">
-        <v>104.57</v>
+        <v>143.36000000000001</v>
       </c>
       <c r="J13">
-        <v>51</v>
+        <v>74.5</v>
       </c>
       <c r="S13" s="3">
         <v>87</v>
@@ -1820,31 +1820,31 @@
         <v>46239</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="F14">
-        <v>0.68469999999999998</v>
+        <v>0.73040000000000005</v>
       </c>
       <c r="G14">
-        <v>0.36359999999999998</v>
+        <v>0.40189999999999998</v>
       </c>
       <c r="H14">
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
       <c r="I14">
-        <v>97.49</v>
+        <v>92.23</v>
       </c>
       <c r="J14">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="S14" s="5">
         <v>86</v>
@@ -1866,31 +1866,31 @@
         <v>46239</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F15">
-        <v>0.70179999999999998</v>
+        <v>0.67889999999999995</v>
       </c>
       <c r="G15">
-        <v>0.38279999999999997</v>
+        <v>0.35410000000000003</v>
       </c>
       <c r="H15">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="I15">
-        <v>86.55</v>
+        <v>107.74</v>
       </c>
       <c r="J15">
-        <v>44.5</v>
+        <v>61.5</v>
       </c>
       <c r="S15" s="3">
         <v>83</v>
@@ -1912,31 +1912,31 @@
         <v>46239</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E16">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F16">
-        <v>0.73629999999999995</v>
+        <v>0.8</v>
       </c>
       <c r="G16">
-        <v>0.3206</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H16">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="I16">
-        <v>91.39</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="J16">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S16" s="5">
         <v>168</v>
@@ -1958,31 +1958,31 @@
         <v>46239</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17">
-        <v>0.99</v>
+        <v>0.09</v>
       </c>
       <c r="F17">
-        <v>0.77080000000000004</v>
+        <v>0.68140000000000001</v>
       </c>
       <c r="G17">
-        <v>0.22839999999999999</v>
+        <v>0.36840000000000001</v>
       </c>
       <c r="H17">
-        <v>1.1299999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="I17">
-        <v>158.16</v>
+        <v>104.57</v>
       </c>
       <c r="J17">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="S17" s="3">
         <v>169</v>
@@ -2004,31 +2004,31 @@
         <v>46239</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>43</v>
       </c>
       <c r="E18">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="F18">
-        <v>0.70909999999999995</v>
+        <v>0.71789999999999998</v>
       </c>
       <c r="G18">
-        <v>0.2407</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H18">
-        <v>1.64</v>
+        <v>0.9</v>
       </c>
       <c r="I18">
-        <v>167.08</v>
+        <v>92.4</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>12.5</v>
       </c>
       <c r="S18" s="5">
         <v>167.5</v>
@@ -2050,31 +2050,31 @@
         <v>46239</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19">
-        <v>0.98</v>
+        <v>0.33</v>
       </c>
       <c r="F19">
-        <v>0.76190000000000002</v>
+        <v>0.72809999999999997</v>
       </c>
       <c r="G19">
-        <v>0.19750000000000001</v>
+        <v>0.36890000000000001</v>
       </c>
       <c r="H19">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="I19">
-        <v>86.97</v>
+        <v>110.72</v>
       </c>
       <c r="J19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="S19" s="3">
         <v>134</v>
@@ -2099,28 +2099,28 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E20">
-        <v>0.91</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F20">
-        <v>0.70830000000000004</v>
+        <v>0.6512</v>
       </c>
       <c r="G20">
-        <v>0.2099</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H20">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="I20">
-        <v>152</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="J20">
-        <v>34.5</v>
+        <v>8.5</v>
       </c>
       <c r="S20" s="5">
         <v>220.5</v>
@@ -2142,31 +2142,31 @@
         <v>46239</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>0.82</v>
+        <v>0.33</v>
       </c>
       <c r="F21">
-        <v>0.75929999999999997</v>
+        <v>0.69350000000000001</v>
       </c>
       <c r="G21">
-        <v>0.25309999999999999</v>
+        <v>0.38219999999999998</v>
       </c>
       <c r="H21">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="I21">
-        <v>151.12</v>
+        <v>101.62</v>
       </c>
       <c r="J21">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="S21" s="3">
         <v>31.5</v>
@@ -2188,31 +2188,31 @@
         <v>46239</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="F22">
-        <v>0.64290000000000003</v>
+        <v>0.77590000000000003</v>
       </c>
       <c r="G22">
-        <v>0.36</v>
+        <v>0.27779999999999999</v>
       </c>
       <c r="H22">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="I22">
-        <v>91.32</v>
+        <v>153.16</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="S22" s="5">
         <v>34</v>
@@ -2234,31 +2234,31 @@
         <v>46239</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>43</v>
       </c>
       <c r="E23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F23">
-        <v>0.6512</v>
+        <v>0.79410000000000003</v>
       </c>
       <c r="G23">
-        <v>0.37330000000000002</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H23">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="I23">
-        <v>76.900000000000006</v>
+        <v>155.13</v>
       </c>
       <c r="J23">
-        <v>8.5</v>
+        <v>83</v>
       </c>
       <c r="S23" s="3">
         <v>34</v>
@@ -2283,28 +2283,28 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24">
-        <v>0.27</v>
+        <v>0.78</v>
       </c>
       <c r="F24">
-        <v>0.5484</v>
+        <v>0.70909999999999995</v>
       </c>
       <c r="G24">
-        <v>0.15110000000000001</v>
+        <v>0.2407</v>
       </c>
       <c r="H24">
-        <v>0.77</v>
+        <v>1.64</v>
       </c>
       <c r="I24">
-        <v>81.209999999999994</v>
+        <v>167.08</v>
       </c>
       <c r="J24">
-        <v>10.5</v>
+        <v>35</v>
       </c>
       <c r="S24" s="5">
         <v>30</v>
@@ -2326,31 +2326,31 @@
         <v>46239</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E25">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="F25">
-        <v>0.69169999999999998</v>
+        <v>0.80279999999999996</v>
       </c>
       <c r="G25">
-        <v>0.36890000000000001</v>
+        <v>0.35189999999999999</v>
       </c>
       <c r="H25">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="I25">
-        <v>86.24</v>
+        <v>156.07</v>
       </c>
       <c r="J25">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="S25" s="3">
         <v>26</v>
@@ -2372,31 +2372,31 @@
         <v>46239</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F26">
-        <v>0.67030000000000001</v>
+        <v>0.70489999999999997</v>
       </c>
       <c r="G26">
-        <v>0.27110000000000001</v>
+        <v>0.41149999999999998</v>
       </c>
       <c r="H26">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="I26">
-        <v>77.62</v>
+        <v>100.42</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="S26" s="5">
         <v>65</v>
@@ -2418,31 +2418,31 @@
         <v>46239</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F27">
-        <v>0.78949999999999998</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="G27">
-        <v>0.28710000000000002</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="H27">
-        <v>0.43</v>
+        <v>0.89</v>
       </c>
       <c r="I27">
-        <v>90.12</v>
+        <v>88.79</v>
       </c>
       <c r="J27">
-        <v>69.5</v>
+        <v>50.5</v>
       </c>
       <c r="S27" s="3">
         <v>51</v>
@@ -2470,25 +2470,25 @@
         <v>11</v>
       </c>
       <c r="D28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28">
         <v>0.13</v>
       </c>
       <c r="F28">
-        <v>0.8</v>
+        <v>0.7802</v>
       </c>
       <c r="G28">
-        <v>0.36359999999999998</v>
+        <v>0.3397</v>
       </c>
       <c r="H28">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="I28">
-        <v>80.010000000000005</v>
+        <v>75.27</v>
       </c>
       <c r="J28">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="S28" s="5">
         <v>47</v>
@@ -2510,7 +2510,7 @@
         <v>46239</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -2519,22 +2519,22 @@
         <v>44</v>
       </c>
       <c r="E29">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F29">
-        <v>0.7802</v>
+        <v>0.68469999999999998</v>
       </c>
       <c r="G29">
-        <v>0.3397</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="H29">
-        <v>0.54</v>
+        <v>0.94</v>
       </c>
       <c r="I29">
-        <v>75.27</v>
+        <v>97.49</v>
       </c>
       <c r="J29">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="S29" s="3">
         <v>51</v>
@@ -2556,31 +2556,31 @@
         <v>46239</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="F30">
-        <v>0.77659999999999996</v>
+        <v>0.66410000000000002</v>
       </c>
       <c r="G30">
-        <v>0.3493</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H30">
-        <v>0.56000000000000005</v>
+        <v>1.2</v>
       </c>
       <c r="I30">
-        <v>78.38</v>
+        <v>99.25</v>
       </c>
       <c r="J30">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="S30" s="5">
         <v>51</v>
@@ -2602,31 +2602,31 @@
         <v>46239</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="F31">
-        <v>0.77659999999999996</v>
+        <v>0.67330000000000001</v>
       </c>
       <c r="G31">
-        <v>0.3493</v>
+        <v>0.30220000000000002</v>
       </c>
       <c r="H31">
-        <v>0.56000000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="I31">
-        <v>78.38</v>
+        <v>103.44</v>
       </c>
       <c r="J31">
-        <v>51</v>
+        <v>20.5</v>
       </c>
       <c r="S31" s="3">
         <v>174</v>
@@ -2648,31 +2648,31 @@
         <v>46239</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="F32">
-        <v>0.84379999999999999</v>
+        <v>0.5484</v>
       </c>
       <c r="G32">
-        <v>0.33329999999999999</v>
+        <v>0.15110000000000001</v>
       </c>
       <c r="H32">
-        <v>1.02</v>
+        <v>0.77</v>
       </c>
       <c r="I32">
-        <v>176.85</v>
+        <v>81.209999999999994</v>
       </c>
       <c r="J32">
-        <v>83</v>
+        <v>10.5</v>
       </c>
       <c r="S32" s="5">
         <v>158</v>
@@ -2694,31 +2694,31 @@
         <v>46239</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E33">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="F33">
-        <v>0.79410000000000003</v>
+        <v>0.7016</v>
       </c>
       <c r="G33">
-        <v>0.33329999999999999</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H33">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="I33">
-        <v>155.13</v>
+        <v>100.75</v>
       </c>
       <c r="J33">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="S33" s="3">
         <v>174</v>
@@ -2740,7 +2740,7 @@
         <v>46239</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -2749,22 +2749,22 @@
         <v>44</v>
       </c>
       <c r="E34">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="F34">
-        <v>0.80600000000000005</v>
+        <v>0.80559999999999998</v>
       </c>
       <c r="G34">
-        <v>0.33329999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="H34">
-        <v>1.33</v>
+        <v>0.72</v>
       </c>
       <c r="I34">
-        <v>192.02</v>
+        <v>133.66</v>
       </c>
       <c r="J34">
-        <v>84.5</v>
+        <v>39</v>
       </c>
       <c r="S34" s="5">
         <v>186.5</v>
@@ -2792,25 +2792,25 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F35">
-        <v>0.81820000000000004</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="G35">
         <v>0.33329999999999999</v>
       </c>
       <c r="H35">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="I35">
-        <v>186.33</v>
+        <v>192.02</v>
       </c>
       <c r="J35">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
       <c r="S35" s="3">
         <v>168</v>
@@ -2832,31 +2832,31 @@
         <v>46239</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36">
-        <v>0.1</v>
+        <v>0.98</v>
       </c>
       <c r="F36">
-        <v>0.7671</v>
+        <v>0.76190000000000002</v>
       </c>
       <c r="G36">
-        <v>0.34570000000000001</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="H36">
-        <v>1.74</v>
+        <v>1.02</v>
       </c>
       <c r="I36">
-        <v>180.27</v>
+        <v>86.97</v>
       </c>
       <c r="J36">
-        <v>82.5</v>
+        <v>17</v>
       </c>
       <c r="S36" s="5">
         <v>37.5</v>
@@ -2878,31 +2878,31 @@
         <v>46239</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E37">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="F37">
-        <v>0.64459999999999995</v>
+        <v>0.78669999999999995</v>
       </c>
       <c r="G37">
-        <v>0.34670000000000001</v>
+        <v>0.36420000000000002</v>
       </c>
       <c r="H37">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="I37">
-        <v>118.59</v>
+        <v>172.68</v>
       </c>
       <c r="J37">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="S37" s="3">
         <v>47</v>
@@ -2924,31 +2924,31 @@
         <v>46239</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D38">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E38">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="F38">
-        <v>0.72809999999999997</v>
+        <v>0.72409999999999997</v>
       </c>
       <c r="G38">
-        <v>0.36890000000000001</v>
+        <v>0.40189999999999998</v>
       </c>
       <c r="H38">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I38">
-        <v>110.72</v>
+        <v>86.82</v>
       </c>
       <c r="J38">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="S38" s="5">
         <v>46</v>
@@ -2973,28 +2973,28 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D39">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E39">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="F39">
-        <v>0.67330000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G39">
-        <v>0.30220000000000002</v>
+        <v>0.3589</v>
       </c>
       <c r="H39">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="I39">
-        <v>103.44</v>
+        <v>89.72</v>
       </c>
       <c r="J39">
-        <v>20.5</v>
+        <v>52</v>
       </c>
       <c r="S39" s="3">
         <v>48.5</v>
@@ -3016,31 +3016,31 @@
         <v>46239</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D40">
         <v>45</v>
       </c>
       <c r="E40">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="F40">
-        <v>0.64290000000000003</v>
+        <v>0.77659999999999996</v>
       </c>
       <c r="G40">
-        <v>0.32</v>
+        <v>0.3493</v>
       </c>
       <c r="H40">
-        <v>1.0900000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I40">
-        <v>127.1</v>
+        <v>78.38</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="S40" s="5">
         <v>49</v>
@@ -3062,31 +3062,31 @@
         <v>46239</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D41">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="F41">
-        <v>0.68930000000000002</v>
+        <v>0.70179999999999998</v>
       </c>
       <c r="G41">
-        <v>0.31559999999999999</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="H41">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I41">
-        <v>104.62</v>
+        <v>86.55</v>
       </c>
       <c r="J41">
-        <v>21</v>
+        <v>44.5</v>
       </c>
       <c r="S41" s="3">
         <v>87.5</v>
@@ -3108,31 +3108,31 @@
         <v>46239</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E42">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="F42">
-        <v>0.70369999999999999</v>
+        <v>0.6694</v>
       </c>
       <c r="G42">
-        <v>0.36359999999999998</v>
+        <v>0.36890000000000001</v>
       </c>
       <c r="H42">
-        <v>0.86</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I42">
-        <v>82.82</v>
+        <v>97.96</v>
       </c>
       <c r="J42">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="S42" s="5">
         <v>92</v>
@@ -3157,28 +3157,28 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E43">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="F43">
-        <v>0.67889999999999995</v>
+        <v>0.64290000000000003</v>
       </c>
       <c r="G43">
-        <v>0.35410000000000003</v>
+        <v>0.32</v>
       </c>
       <c r="H43">
-        <v>0.94</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="I43">
-        <v>107.74</v>
+        <v>127.1</v>
       </c>
       <c r="J43">
-        <v>61.5</v>
+        <v>30</v>
       </c>
       <c r="S43" s="3">
         <v>85</v>
@@ -3200,31 +3200,31 @@
         <v>46239</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>45</v>
+      </c>
+      <c r="E44">
+        <v>0.08</v>
+      </c>
+      <c r="F44">
+        <v>0.69169999999999998</v>
+      </c>
+      <c r="G44">
+        <v>0.36890000000000001</v>
+      </c>
+      <c r="H44">
+        <v>1.01</v>
+      </c>
+      <c r="I44">
+        <v>86.24</v>
+      </c>
+      <c r="J44">
         <v>11</v>
-      </c>
-      <c r="D44">
-        <v>44</v>
-      </c>
-      <c r="E44">
-        <v>0.17</v>
-      </c>
-      <c r="F44">
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="G44">
-        <v>0.38279999999999997</v>
-      </c>
-      <c r="H44">
-        <v>0.89</v>
-      </c>
-      <c r="I44">
-        <v>88.79</v>
-      </c>
-      <c r="J44">
-        <v>50.5</v>
       </c>
       <c r="S44" s="5">
         <v>90</v>
@@ -3246,31 +3246,31 @@
         <v>46239</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>45</v>
       </c>
       <c r="E45">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="F45">
-        <v>0.75</v>
+        <v>0.75680000000000003</v>
       </c>
       <c r="G45">
-        <v>0.3589</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="H45">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="I45">
-        <v>89.72</v>
+        <v>104.87</v>
       </c>
       <c r="J45">
-        <v>52</v>
+        <v>16.5</v>
       </c>
       <c r="S45" s="3">
         <v>88</v>
@@ -3292,28 +3292,28 @@
         <v>46239</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="F46">
-        <v>0.73960000000000004</v>
+        <v>0.8085</v>
       </c>
       <c r="G46">
-        <v>0.3397</v>
+        <v>0.2346</v>
       </c>
       <c r="H46">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="I46">
-        <v>93.24</v>
+        <v>168.13</v>
       </c>
       <c r="J46">
         <v>38</v>
@@ -3338,31 +3338,31 @@
         <v>46239</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
       </c>
       <c r="D47">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E47">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="F47">
-        <v>0.78049999999999997</v>
+        <v>0.81820000000000004</v>
       </c>
       <c r="G47">
-        <v>0.19750000000000001</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="H47">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="I47">
-        <v>119.44</v>
+        <v>186.33</v>
       </c>
       <c r="J47">
-        <v>40.5</v>
+        <v>83.5</v>
       </c>
       <c r="S47" s="3">
         <v>243</v>
@@ -3384,31 +3384,31 @@
         <v>46239</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>0.44</v>
+        <v>0.91</v>
       </c>
       <c r="F48">
-        <v>0.77590000000000003</v>
+        <v>0.70830000000000004</v>
       </c>
       <c r="G48">
-        <v>0.27779999999999999</v>
+        <v>0.2099</v>
       </c>
       <c r="H48">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>153.16</v>
+        <v>152</v>
       </c>
       <c r="J48">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="S48" s="5">
         <v>184</v>
@@ -3430,31 +3430,31 @@
         <v>46239</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
       </c>
       <c r="D49">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="F49">
-        <v>0.80559999999999998</v>
+        <v>0.73129999999999995</v>
       </c>
       <c r="G49">
-        <v>0.17899999999999999</v>
+        <v>0.30249999999999999</v>
       </c>
       <c r="H49">
-        <v>0.72</v>
+        <v>1.84</v>
       </c>
       <c r="I49">
-        <v>133.66</v>
+        <v>148.1</v>
       </c>
       <c r="J49">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="S49" s="3">
         <v>229</v>
@@ -3479,28 +3479,28 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="F50">
-        <v>0.8085</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="G50">
-        <v>0.2346</v>
+        <v>0.44019999999999998</v>
       </c>
       <c r="H50">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="I50">
-        <v>168.13</v>
+        <v>73.319999999999993</v>
       </c>
       <c r="J50">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S50" s="5">
         <v>246</v>
@@ -3522,31 +3522,31 @@
         <v>46239</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51">
         <v>46</v>
       </c>
       <c r="E51">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="F51">
-        <v>0.77359999999999995</v>
+        <v>0.73960000000000004</v>
       </c>
       <c r="G51">
-        <v>0.25309999999999999</v>
+        <v>0.3397</v>
       </c>
       <c r="H51">
-        <v>1.23</v>
+        <v>0.67</v>
       </c>
       <c r="I51">
-        <v>170</v>
+        <v>93.24</v>
       </c>
       <c r="J51">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="S51" s="3">
         <v>30.5</v>
@@ -3568,31 +3568,31 @@
         <v>46239</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D52">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E52">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F52">
-        <v>0.69399999999999995</v>
+        <v>0.77659999999999996</v>
       </c>
       <c r="G52">
-        <v>0.4133</v>
+        <v>0.3493</v>
       </c>
       <c r="H52">
-        <v>1.1200000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I52">
-        <v>93.43</v>
+        <v>78.38</v>
       </c>
       <c r="J52">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="S52" s="5">
         <v>39</v>
@@ -3614,31 +3614,31 @@
         <v>46239</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D53">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E53">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="F53">
-        <v>0.71789999999999998</v>
+        <v>0.73629999999999995</v>
       </c>
       <c r="G53">
-        <v>0.37330000000000002</v>
+        <v>0.3206</v>
       </c>
       <c r="H53">
-        <v>0.9</v>
+        <v>0.64</v>
       </c>
       <c r="I53">
-        <v>92.4</v>
+        <v>91.39</v>
       </c>
       <c r="J53">
-        <v>12.5</v>
+        <v>51</v>
       </c>
       <c r="S53" s="3">
         <v>36</v>
@@ -3666,25 +3666,25 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E54">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F54">
-        <v>0.66410000000000002</v>
+        <v>0.7319</v>
       </c>
       <c r="G54">
-        <v>0.38669999999999999</v>
+        <v>0.44890000000000002</v>
       </c>
       <c r="H54">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="I54">
-        <v>99.25</v>
+        <v>102.67</v>
       </c>
       <c r="J54">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="S54" s="5">
         <v>41.5</v>
@@ -3706,31 +3706,31 @@
         <v>46239</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
       </c>
       <c r="D55">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E55">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="F55">
-        <v>0.6694</v>
+        <v>0.68930000000000002</v>
       </c>
       <c r="G55">
-        <v>0.36890000000000001</v>
+        <v>0.31559999999999999</v>
       </c>
       <c r="H55">
-        <v>1.1200000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="I55">
-        <v>97.96</v>
+        <v>104.62</v>
       </c>
       <c r="J55">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S55" s="3">
         <v>37</v>
@@ -3752,7 +3752,7 @@
         <v>46239</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
@@ -3761,22 +3761,22 @@
         <v>46</v>
       </c>
       <c r="E56">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="F56">
-        <v>0.7319</v>
+        <v>0.67030000000000001</v>
       </c>
       <c r="G56">
-        <v>0.44890000000000002</v>
+        <v>0.27110000000000001</v>
       </c>
       <c r="H56">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="I56">
-        <v>102.67</v>
+        <v>77.62</v>
       </c>
       <c r="J56">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S56" s="5">
         <v>71</v>
@@ -3798,31 +3798,31 @@
         <v>46239</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D57">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E57">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="F57">
-        <v>0.7177</v>
+        <v>0.6583</v>
       </c>
       <c r="G57">
-        <v>0.42580000000000001</v>
+        <v>0.35110000000000002</v>
       </c>
       <c r="H57">
-        <v>0.94</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I57">
-        <v>95.7</v>
+        <v>87.99</v>
       </c>
       <c r="J57">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="S57" s="3">
         <v>67</v>
@@ -3847,28 +3847,28 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D58">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E58">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="F58">
-        <v>0.73040000000000005</v>
+        <v>0.77359999999999995</v>
       </c>
       <c r="G58">
-        <v>0.40189999999999998</v>
+        <v>0.25309999999999999</v>
       </c>
       <c r="H58">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="I58">
-        <v>92.23</v>
+        <v>170</v>
       </c>
       <c r="J58">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="S58" s="5">
         <v>72.5</v>
@@ -3890,31 +3890,31 @@
         <v>46239</v>
       </c>
       <c r="B59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D59">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E59">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F59">
-        <v>0.70489999999999997</v>
+        <v>0.7671</v>
       </c>
       <c r="G59">
-        <v>0.41149999999999998</v>
+        <v>0.34570000000000001</v>
       </c>
       <c r="H59">
-        <v>0.97</v>
+        <v>1.74</v>
       </c>
       <c r="I59">
-        <v>100.42</v>
+        <v>180.27</v>
       </c>
       <c r="J59">
-        <v>55</v>
+        <v>82.5</v>
       </c>
       <c r="S59" s="3">
         <v>61.5</v>
@@ -3936,31 +3936,31 @@
         <v>46239</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D60">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E60">
-        <v>0.15</v>
+        <v>0.82</v>
       </c>
       <c r="F60">
-        <v>0.72409999999999997</v>
+        <v>0.75929999999999997</v>
       </c>
       <c r="G60">
-        <v>0.40189999999999998</v>
+        <v>0.25309999999999999</v>
       </c>
       <c r="H60">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="I60">
-        <v>86.82</v>
+        <v>151.12</v>
       </c>
       <c r="J60">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="S60" s="5">
         <v>65</v>
@@ -3982,42 +3982,42 @@
         <v>46239</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <v>46</v>
       </c>
       <c r="E61">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F61">
-        <v>0.73599999999999999</v>
+        <v>0.78569999999999995</v>
       </c>
       <c r="G61">
-        <v>0.44019999999999998</v>
+        <v>0.33950000000000002</v>
       </c>
       <c r="H61">
-        <v>0.89</v>
+        <v>1.54</v>
       </c>
       <c r="I61">
-        <v>73.319999999999993</v>
+        <v>147.53</v>
       </c>
       <c r="J61">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U61" s="6">
         <f>AVERAGE(표2[Median LT])</f>
-        <v>114.21066666666664</v>
+        <v>114.21066666666667</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="I62">
         <f>AVERAGE(표2[Median LT])</f>
-        <v>114.21066666666664</v>
+        <v>114.21066666666667</v>
       </c>
     </row>
   </sheetData>
